--- a/Externals/Assignment of Week 10.xlsx
+++ b/Externals/Assignment of Week 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kemenkeu-my.sharepoint.com/personal/teuku_radarma_kemenkeu_go_id/Documents/PKN STAN/Audit SI/Externals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD47B63E-B202-4E7B-A7D6-35A1669F1230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{CD47B63E-B202-4E7B-A7D6-35A1669F1230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC13727A-4B4D-4A1E-B415-CC20754384A2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{4F872A5E-A3F8-4E20-8B3D-7EC9632297D7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{4F872A5E-A3F8-4E20-8B3D-7EC9632297D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="566">
   <si>
     <t>AUTHOR</t>
   </si>
@@ -1316,9 +1316,6 @@
     <t>S-25060013</t>
   </si>
   <si>
-    <t>S-25060014</t>
-  </si>
-  <si>
     <t>S-25060015</t>
   </si>
   <si>
@@ -1421,9 +1418,6 @@
     <t>S-25080005</t>
   </si>
   <si>
-    <t>S-25080006</t>
-  </si>
-  <si>
     <t>S-25080007</t>
   </si>
   <si>
@@ -1728,6 +1722,24 @@
   </si>
   <si>
     <t>S-25120012</t>
+  </si>
+  <si>
+    <t>310000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 360000</t>
+  </si>
+  <si>
+    <t>S-25080000</t>
+  </si>
+  <si>
+    <t>06908447</t>
+  </si>
+  <si>
+    <t>29/02/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4</t>
   </si>
 </sst>
 </file>
@@ -1763,9 +1775,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3516,6 +3535,9 @@
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -3542,8 +3564,8 @@
       <c r="B2" t="s">
         <v>307</v>
       </c>
-      <c r="C2">
-        <v>5109258</v>
+      <c r="C2" t="s">
+        <v>266</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4025,7 +4047,7 @@
         <v>4</v>
       </c>
       <c r="E30">
-        <v>1240000</v>
+        <v>1540000</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -4216,8 +4238,8 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>45716</v>
+      <c r="A42" s="4" t="s">
+        <v>564</v>
       </c>
       <c r="B42" t="s">
         <v>347</v>
@@ -4226,10 +4248,10 @@
         <v>257</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>340000</v>
+        <v>1040000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -5452,8 +5474,8 @@
       <c r="D114">
         <v>2</v>
       </c>
-      <c r="E114">
-        <v>360000</v>
+      <c r="E114" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
@@ -5469,8 +5491,8 @@
       <c r="D115">
         <v>1</v>
       </c>
-      <c r="E115">
-        <v>310000</v>
+      <c r="E115" s="3" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
@@ -5529,7 +5551,7 @@
         <v>45827</v>
       </c>
       <c r="B119" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C119" t="s">
         <v>274</v>
@@ -5546,7 +5568,7 @@
         <v>45828</v>
       </c>
       <c r="B120" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C120" t="s">
         <v>306</v>
@@ -5563,7 +5585,7 @@
         <v>45830</v>
       </c>
       <c r="B121" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C121" t="s">
         <v>258</v>
@@ -5580,7 +5602,7 @@
         <v>45831</v>
       </c>
       <c r="B122" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C122" t="s">
         <v>305</v>
@@ -5597,7 +5619,7 @@
         <v>45834</v>
       </c>
       <c r="B123" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C123" t="s">
         <v>233</v>
@@ -5614,7 +5636,7 @@
         <v>45835</v>
       </c>
       <c r="B124" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C124" t="s">
         <v>302</v>
@@ -5631,7 +5653,7 @@
         <v>45836</v>
       </c>
       <c r="B125" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C125" t="s">
         <v>257</v>
@@ -5648,7 +5670,7 @@
         <v>45837</v>
       </c>
       <c r="B126" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C126" t="s">
         <v>297</v>
@@ -5665,7 +5687,7 @@
         <v>45838</v>
       </c>
       <c r="B127" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C127" t="s">
         <v>262</v>
@@ -5682,7 +5704,7 @@
         <v>45839</v>
       </c>
       <c r="B128" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C128" t="s">
         <v>209</v>
@@ -5699,7 +5721,7 @@
         <v>45840</v>
       </c>
       <c r="B129" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C129" t="s">
         <v>288</v>
@@ -5716,7 +5738,7 @@
         <v>45841</v>
       </c>
       <c r="B130" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C130" t="s">
         <v>267</v>
@@ -5733,7 +5755,7 @@
         <v>45844</v>
       </c>
       <c r="B131" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C131" t="s">
         <v>239</v>
@@ -5750,7 +5772,7 @@
         <v>45845</v>
       </c>
       <c r="B132" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C132" t="s">
         <v>237</v>
@@ -5767,7 +5789,7 @@
         <v>45848</v>
       </c>
       <c r="B133" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C133" t="s">
         <v>303</v>
@@ -5784,7 +5806,7 @@
         <v>45849</v>
       </c>
       <c r="B134" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C134" t="s">
         <v>266</v>
@@ -5801,7 +5823,7 @@
         <v>45850</v>
       </c>
       <c r="B135" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C135" t="s">
         <v>222</v>
@@ -5818,7 +5840,7 @@
         <v>45851</v>
       </c>
       <c r="B136" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C136" t="s">
         <v>271</v>
@@ -5835,7 +5857,7 @@
         <v>45854</v>
       </c>
       <c r="B137" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C137" t="s">
         <v>253</v>
@@ -5852,7 +5874,7 @@
         <v>45855</v>
       </c>
       <c r="B138" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C138" t="s">
         <v>243</v>
@@ -5869,7 +5891,7 @@
         <v>45856</v>
       </c>
       <c r="B139" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C139" t="s">
         <v>279</v>
@@ -5886,7 +5908,7 @@
         <v>45857</v>
       </c>
       <c r="B140" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C140" t="s">
         <v>254</v>
@@ -5903,7 +5925,7 @@
         <v>45858</v>
       </c>
       <c r="B141" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C141" t="s">
         <v>243</v>
@@ -5920,7 +5942,7 @@
         <v>45859</v>
       </c>
       <c r="B142" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C142" t="s">
         <v>262</v>
@@ -5937,7 +5959,7 @@
         <v>45860</v>
       </c>
       <c r="B143" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C143" t="s">
         <v>210</v>
@@ -5954,7 +5976,7 @@
         <v>45861</v>
       </c>
       <c r="B144" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C144" t="s">
         <v>305</v>
@@ -5971,7 +5993,7 @@
         <v>45864</v>
       </c>
       <c r="B145" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C145" t="s">
         <v>220</v>
@@ -5988,7 +6010,7 @@
         <v>45865</v>
       </c>
       <c r="B146" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C146" t="s">
         <v>231</v>
@@ -6005,7 +6027,7 @@
         <v>45866</v>
       </c>
       <c r="B147" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C147" t="s">
         <v>227</v>
@@ -6022,7 +6044,7 @@
         <v>45867</v>
       </c>
       <c r="B148" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C148" t="s">
         <v>270</v>
@@ -6039,7 +6061,7 @@
         <v>45870</v>
       </c>
       <c r="B149" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C149" t="s">
         <v>238</v>
@@ -6056,7 +6078,7 @@
         <v>45872</v>
       </c>
       <c r="B150" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C150" t="s">
         <v>254</v>
@@ -6073,7 +6095,7 @@
         <v>45873</v>
       </c>
       <c r="B151" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C151" t="s">
         <v>232</v>
@@ -6090,7 +6112,7 @@
         <v>45874</v>
       </c>
       <c r="B152" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C152" t="s">
         <v>258</v>
@@ -6107,7 +6129,7 @@
         <v>45875</v>
       </c>
       <c r="B153" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C153" t="s">
         <v>276</v>
@@ -6124,10 +6146,10 @@
         <v>45878</v>
       </c>
       <c r="B154" t="s">
-        <v>459</v>
-      </c>
-      <c r="C154" t="s">
-        <v>303</v>
+        <v>562</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="D154">
         <v>4</v>
@@ -6141,7 +6163,7 @@
         <v>45880</v>
       </c>
       <c r="B155" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C155" t="s">
         <v>217</v>
@@ -6158,7 +6180,7 @@
         <v>45881</v>
       </c>
       <c r="B156" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C156" t="s">
         <v>282</v>
@@ -6175,7 +6197,7 @@
         <v>45882</v>
       </c>
       <c r="B157" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C157" t="s">
         <v>222</v>
@@ -6192,7 +6214,7 @@
         <v>45883</v>
       </c>
       <c r="B158" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C158" t="s">
         <v>301</v>
@@ -6209,7 +6231,7 @@
         <v>45884</v>
       </c>
       <c r="B159" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C159" t="s">
         <v>296</v>
@@ -6226,7 +6248,7 @@
         <v>45885</v>
       </c>
       <c r="B160" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C160" t="s">
         <v>281</v>
@@ -6243,7 +6265,7 @@
         <v>45886</v>
       </c>
       <c r="B161" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C161" t="s">
         <v>294</v>
@@ -6260,7 +6282,7 @@
         <v>45887</v>
       </c>
       <c r="B162" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C162" t="s">
         <v>246</v>
@@ -6277,7 +6299,7 @@
         <v>45888</v>
       </c>
       <c r="B163" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C163" t="s">
         <v>278</v>
@@ -6294,7 +6316,7 @@
         <v>45889</v>
       </c>
       <c r="B164" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C164" t="s">
         <v>255</v>
@@ -6311,7 +6333,7 @@
         <v>45890</v>
       </c>
       <c r="B165" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C165" t="s">
         <v>272</v>
@@ -6328,7 +6350,7 @@
         <v>45891</v>
       </c>
       <c r="B166" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C166" t="s">
         <v>256</v>
@@ -6345,7 +6367,7 @@
         <v>45892</v>
       </c>
       <c r="B167" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C167" t="s">
         <v>217</v>
@@ -6362,7 +6384,7 @@
         <v>45893</v>
       </c>
       <c r="B168" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C168" t="s">
         <v>228</v>
@@ -6379,7 +6401,7 @@
         <v>45894</v>
       </c>
       <c r="B169" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C169" t="s">
         <v>227</v>
@@ -6396,7 +6418,7 @@
         <v>45895</v>
       </c>
       <c r="B170" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C170" t="s">
         <v>279</v>
@@ -6413,7 +6435,7 @@
         <v>45896</v>
       </c>
       <c r="B171" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C171" t="s">
         <v>275</v>
@@ -6430,7 +6452,7 @@
         <v>45897</v>
       </c>
       <c r="B172" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C172" t="s">
         <v>252</v>
@@ -6447,7 +6469,7 @@
         <v>45898</v>
       </c>
       <c r="B173" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C173" t="s">
         <v>257</v>
@@ -6464,7 +6486,7 @@
         <v>45900</v>
       </c>
       <c r="B174" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C174" t="s">
         <v>269</v>
@@ -6481,7 +6503,7 @@
         <v>45901</v>
       </c>
       <c r="B175" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C175" t="s">
         <v>277</v>
@@ -6498,7 +6520,7 @@
         <v>45904</v>
       </c>
       <c r="B176" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C176" t="s">
         <v>221</v>
@@ -6515,7 +6537,7 @@
         <v>45905</v>
       </c>
       <c r="B177" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C177" t="s">
         <v>221</v>
@@ -6532,7 +6554,7 @@
         <v>45906</v>
       </c>
       <c r="B178" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C178" t="s">
         <v>281</v>
@@ -6549,7 +6571,7 @@
         <v>45908</v>
       </c>
       <c r="B179" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C179" t="s">
         <v>263</v>
@@ -6566,7 +6588,7 @@
         <v>45909</v>
       </c>
       <c r="B180" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C180" t="s">
         <v>285</v>
@@ -6583,7 +6605,7 @@
         <v>45910</v>
       </c>
       <c r="B181" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C181" t="s">
         <v>273</v>
@@ -6600,7 +6622,7 @@
         <v>45911</v>
       </c>
       <c r="B182" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C182" t="s">
         <v>228</v>
@@ -6617,7 +6639,7 @@
         <v>45912</v>
       </c>
       <c r="B183" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C183" t="s">
         <v>246</v>
@@ -6634,7 +6656,7 @@
         <v>45913</v>
       </c>
       <c r="B184" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C184" t="s">
         <v>222</v>
@@ -6651,7 +6673,7 @@
         <v>45914</v>
       </c>
       <c r="B185" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C185" t="s">
         <v>243</v>
@@ -6668,7 +6690,7 @@
         <v>45916</v>
       </c>
       <c r="B186" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C186" t="s">
         <v>290</v>
@@ -6685,7 +6707,7 @@
         <v>45917</v>
       </c>
       <c r="B187" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C187" t="s">
         <v>299</v>
@@ -6702,7 +6724,7 @@
         <v>45918</v>
       </c>
       <c r="B188" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C188" t="s">
         <v>257</v>
@@ -6719,7 +6741,7 @@
         <v>45919</v>
       </c>
       <c r="B189" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C189" t="s">
         <v>294</v>
@@ -6736,7 +6758,7 @@
         <v>45920</v>
       </c>
       <c r="B190" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C190" t="s">
         <v>294</v>
@@ -6753,7 +6775,7 @@
         <v>45923</v>
       </c>
       <c r="B191" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C191" t="s">
         <v>288</v>
@@ -6770,7 +6792,7 @@
         <v>45924</v>
       </c>
       <c r="B192" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C192" t="s">
         <v>295</v>
@@ -6787,7 +6809,7 @@
         <v>45925</v>
       </c>
       <c r="B193" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C193" t="s">
         <v>229</v>
@@ -6804,7 +6826,7 @@
         <v>45926</v>
       </c>
       <c r="B194" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C194" t="s">
         <v>283</v>
@@ -6821,7 +6843,7 @@
         <v>45928</v>
       </c>
       <c r="B195" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C195" t="s">
         <v>241</v>
@@ -6838,7 +6860,7 @@
         <v>45929</v>
       </c>
       <c r="B196" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C196" t="s">
         <v>242</v>
@@ -6855,7 +6877,7 @@
         <v>45930</v>
       </c>
       <c r="B197" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C197" t="s">
         <v>300</v>
@@ -6872,7 +6894,7 @@
         <v>45932</v>
       </c>
       <c r="B198" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C198" t="s">
         <v>284</v>
@@ -6889,7 +6911,7 @@
         <v>45933</v>
       </c>
       <c r="B199" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C199" t="s">
         <v>223</v>
@@ -6906,7 +6928,7 @@
         <v>45934</v>
       </c>
       <c r="B200" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C200" t="s">
         <v>304</v>
@@ -6923,7 +6945,7 @@
         <v>45935</v>
       </c>
       <c r="B201" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C201" t="s">
         <v>268</v>
@@ -6940,7 +6962,7 @@
         <v>45936</v>
       </c>
       <c r="B202" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C202" t="s">
         <v>288</v>
@@ -6957,7 +6979,7 @@
         <v>45937</v>
       </c>
       <c r="B203" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C203" t="s">
         <v>214</v>
@@ -6974,7 +6996,7 @@
         <v>45939</v>
       </c>
       <c r="B204" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C204" t="s">
         <v>287</v>
@@ -6991,7 +7013,7 @@
         <v>45941</v>
       </c>
       <c r="B205" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C205" t="s">
         <v>247</v>
@@ -7008,7 +7030,7 @@
         <v>45942</v>
       </c>
       <c r="B206" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C206" t="s">
         <v>275</v>
@@ -7025,7 +7047,7 @@
         <v>45943</v>
       </c>
       <c r="B207" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C207" t="s">
         <v>305</v>
@@ -7042,7 +7064,7 @@
         <v>45944</v>
       </c>
       <c r="B208" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C208" t="s">
         <v>267</v>
@@ -7059,7 +7081,7 @@
         <v>45947</v>
       </c>
       <c r="B209" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C209" t="s">
         <v>259</v>
@@ -7076,7 +7098,7 @@
         <v>45948</v>
       </c>
       <c r="B210" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C210" t="s">
         <v>290</v>
@@ -7093,7 +7115,7 @@
         <v>45949</v>
       </c>
       <c r="B211" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C211" t="s">
         <v>260</v>
@@ -7110,7 +7132,7 @@
         <v>45950</v>
       </c>
       <c r="B212" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C212" t="s">
         <v>290</v>
@@ -7127,7 +7149,7 @@
         <v>45951</v>
       </c>
       <c r="B213" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C213" t="s">
         <v>273</v>
@@ -7144,7 +7166,7 @@
         <v>45952</v>
       </c>
       <c r="B214" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C214" t="s">
         <v>295</v>
@@ -7161,7 +7183,7 @@
         <v>45954</v>
       </c>
       <c r="B215" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C215" t="s">
         <v>236</v>
@@ -7178,7 +7200,7 @@
         <v>45955</v>
       </c>
       <c r="B216" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C216" t="s">
         <v>264</v>
@@ -7195,7 +7217,7 @@
         <v>45956</v>
       </c>
       <c r="B217" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C217" t="s">
         <v>259</v>
@@ -7212,7 +7234,7 @@
         <v>45957</v>
       </c>
       <c r="B218" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C218" t="s">
         <v>243</v>
@@ -7229,7 +7251,7 @@
         <v>45958</v>
       </c>
       <c r="B219" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C219" t="s">
         <v>255</v>
@@ -7246,7 +7268,7 @@
         <v>45959</v>
       </c>
       <c r="B220" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C220" t="s">
         <v>253</v>
@@ -7263,7 +7285,7 @@
         <v>45960</v>
       </c>
       <c r="B221" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C221" t="s">
         <v>260</v>
@@ -7280,7 +7302,7 @@
         <v>45963</v>
       </c>
       <c r="B222" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C222" t="s">
         <v>210</v>
@@ -7297,7 +7319,7 @@
         <v>45964</v>
       </c>
       <c r="B223" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C223" t="s">
         <v>241</v>
@@ -7314,7 +7336,7 @@
         <v>45967</v>
       </c>
       <c r="B224" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C224" t="s">
         <v>303</v>
@@ -7331,7 +7353,7 @@
         <v>45968</v>
       </c>
       <c r="B225" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C225" t="s">
         <v>290</v>
@@ -7348,13 +7370,13 @@
         <v>45969</v>
       </c>
       <c r="B226" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C226" t="s">
         <v>263</v>
       </c>
-      <c r="D226">
-        <v>4</v>
+      <c r="D226" s="3" t="s">
+        <v>565</v>
       </c>
       <c r="E226">
         <v>1200000</v>
@@ -7365,7 +7387,7 @@
         <v>45970</v>
       </c>
       <c r="B227" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C227" t="s">
         <v>228</v>
@@ -7382,7 +7404,7 @@
         <v>45972</v>
       </c>
       <c r="B228" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C228" t="s">
         <v>283</v>
@@ -7399,7 +7421,7 @@
         <v>45974</v>
       </c>
       <c r="B229" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C229" t="s">
         <v>258</v>
@@ -7416,7 +7438,7 @@
         <v>45975</v>
       </c>
       <c r="B230" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C230" t="s">
         <v>287</v>
@@ -7433,7 +7455,7 @@
         <v>45976</v>
       </c>
       <c r="B231" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C231" t="s">
         <v>291</v>
@@ -7450,7 +7472,7 @@
         <v>45978</v>
       </c>
       <c r="B232" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C232" t="s">
         <v>269</v>
@@ -7467,7 +7489,7 @@
         <v>45979</v>
       </c>
       <c r="B233" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C233" t="s">
         <v>298</v>
@@ -7484,7 +7506,7 @@
         <v>45980</v>
       </c>
       <c r="B234" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C234" t="s">
         <v>248</v>
@@ -7501,7 +7523,7 @@
         <v>45981</v>
       </c>
       <c r="B235" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C235" t="s">
         <v>273</v>
@@ -7518,7 +7540,7 @@
         <v>45982</v>
       </c>
       <c r="B236" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C236" t="s">
         <v>209</v>
@@ -7535,7 +7557,7 @@
         <v>45983</v>
       </c>
       <c r="B237" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C237" t="s">
         <v>241</v>
@@ -7552,7 +7574,7 @@
         <v>45984</v>
       </c>
       <c r="B238" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C238" t="s">
         <v>254</v>
@@ -7569,7 +7591,7 @@
         <v>45986</v>
       </c>
       <c r="B239" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C239" t="s">
         <v>228</v>
@@ -7586,7 +7608,7 @@
         <v>45987</v>
       </c>
       <c r="B240" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C240" t="s">
         <v>256</v>
@@ -7603,7 +7625,7 @@
         <v>45988</v>
       </c>
       <c r="B241" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C241" t="s">
         <v>261</v>
@@ -7620,7 +7642,7 @@
         <v>45989</v>
       </c>
       <c r="B242" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C242" t="s">
         <v>291</v>
@@ -7637,7 +7659,7 @@
         <v>45990</v>
       </c>
       <c r="B243" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C243" t="s">
         <v>225</v>
@@ -7654,7 +7676,7 @@
         <v>45991</v>
       </c>
       <c r="B244" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C244" t="s">
         <v>274</v>
@@ -7671,7 +7693,7 @@
         <v>45992</v>
       </c>
       <c r="B245" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C245" t="s">
         <v>230</v>
@@ -7688,7 +7710,7 @@
         <v>45993</v>
       </c>
       <c r="B246" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C246" t="s">
         <v>212</v>
@@ -7705,7 +7727,7 @@
         <v>45994</v>
       </c>
       <c r="B247" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C247" t="s">
         <v>237</v>
@@ -7722,7 +7744,7 @@
         <v>45995</v>
       </c>
       <c r="B248" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C248" t="s">
         <v>253</v>
@@ -7739,7 +7761,7 @@
         <v>45996</v>
       </c>
       <c r="B249" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C249" t="s">
         <v>278</v>
@@ -7756,7 +7778,7 @@
         <v>45997</v>
       </c>
       <c r="B250" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C250" t="s">
         <v>278</v>
@@ -7773,7 +7795,7 @@
         <v>45998</v>
       </c>
       <c r="B251" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C251" t="s">
         <v>304</v>
@@ -7790,7 +7812,7 @@
         <v>46001</v>
       </c>
       <c r="B252" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C252" t="s">
         <v>248</v>
@@ -7807,7 +7829,7 @@
         <v>46004</v>
       </c>
       <c r="B253" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C253" t="s">
         <v>237</v>
@@ -7824,7 +7846,7 @@
         <v>46005</v>
       </c>
       <c r="B254" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C254" t="s">
         <v>227</v>
@@ -7841,7 +7863,7 @@
         <v>46007</v>
       </c>
       <c r="B255" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C255" t="s">
         <v>231</v>
@@ -7858,7 +7880,7 @@
         <v>46008</v>
       </c>
       <c r="B256" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C256" t="s">
         <v>236</v>
@@ -7872,5 +7894,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E114:E115 C2:C154 C155:C256 D226" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Externals/Assignment of Week 10.xlsx
+++ b/Externals/Assignment of Week 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kemenkeu-my.sharepoint.com/personal/teuku_radarma_kemenkeu_go_id/Documents/PKN STAN/Audit SI/Externals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{CD47B63E-B202-4E7B-A7D6-35A1669F1230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC13727A-4B4D-4A1E-B415-CC20754384A2}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{CD47B63E-B202-4E7B-A7D6-35A1669F1230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65FF89E1-F11D-49F7-873A-04E00AED2468}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{4F872A5E-A3F8-4E20-8B3D-7EC9632297D7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{4F872A5E-A3F8-4E20-8B3D-7EC9632297D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
@@ -2100,15 +2100,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD604EB-910E-418A-9BEC-0523D5048D28}">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
+    <col min="3" max="3" width="28.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>207</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>208</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>209</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>210</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>211</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>212</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>213</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>214</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>215</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>216</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>217</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>219</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>220</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>221</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>222</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>223</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>224</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>225</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>226</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>227</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>229</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>230</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>231</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>232</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>233</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>235</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>236</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>237</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>238</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>239</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>240</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>241</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>242</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>243</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>244</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>245</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>246</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>247</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>248</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>249</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>250</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>251</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>252</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>253</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>254</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>255</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>256</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>257</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>258</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>259</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>260</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>261</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>262</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>263</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>264</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>265</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>266</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>267</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>268</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>269</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>270</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>271</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>272</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>273</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>274</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>275</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>276</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>277</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>278</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>279</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>280</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>281</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>282</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>283</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>284</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>285</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>286</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>287</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>288</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>289</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>290</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>291</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>292</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>293</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>294</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>295</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>296</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>297</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>298</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>299</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>300</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>301</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>302</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>303</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>304</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>305</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>306</v>
       </c>
@@ -3523,7 +3523,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B101" xr:uid="{7AD604EB-910E-418A-9BEC-0523D5048D28}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3531,16 +3530,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742C12A7-CB97-4FC4-949D-D2F8ACB81608}">
   <dimension ref="A1:E256"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>206</v>
       </c>
@@ -3557,7 +3556,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>45661</v>
       </c>
@@ -3574,7 +3573,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>45662</v>
       </c>
@@ -3591,7 +3590,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>45663</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>45664</v>
       </c>
@@ -3625,7 +3624,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>45665</v>
       </c>
@@ -3642,7 +3641,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>45666</v>
       </c>
@@ -3659,7 +3658,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>45667</v>
       </c>
@@ -3676,7 +3675,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>45668</v>
       </c>
@@ -3693,7 +3692,7 @@
         <v>570000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>45669</v>
       </c>
@@ -3710,7 +3709,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>45670</v>
       </c>
@@ -3727,7 +3726,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>45673</v>
       </c>
@@ -3744,7 +3743,7 @@
         <v>1020000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>45675</v>
       </c>
@@ -3761,7 +3760,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>45676</v>
       </c>
@@ -3778,7 +3777,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>45679</v>
       </c>
@@ -3795,7 +3794,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>45680</v>
       </c>
@@ -3812,7 +3811,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>45683</v>
       </c>
@@ -3829,7 +3828,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>45684</v>
       </c>
@@ -3846,7 +3845,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>45685</v>
       </c>
@@ -3863,7 +3862,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>45686</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>45687</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>420000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>45688</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>660000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>45689</v>
       </c>
@@ -3931,7 +3930,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>45691</v>
       </c>
@@ -3948,7 +3947,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>45692</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>45693</v>
       </c>
@@ -3982,7 +3981,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>45696</v>
       </c>
@@ -3999,7 +3998,7 @@
         <v>520000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>45697</v>
       </c>
@@ -4016,7 +4015,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>45698</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>45701</v>
       </c>
@@ -4050,7 +4049,7 @@
         <v>1540000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>45704</v>
       </c>
@@ -4067,7 +4066,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>45705</v>
       </c>
@@ -4084,7 +4083,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>45706</v>
       </c>
@@ -4101,7 +4100,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>45707</v>
       </c>
@@ -4118,7 +4117,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>45708</v>
       </c>
@@ -4135,7 +4134,7 @@
         <v>420000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>45709</v>
       </c>
@@ -4152,7 +4151,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>45710</v>
       </c>
@@ -4169,7 +4168,7 @@
         <v>420000</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>45711</v>
       </c>
@@ -4186,7 +4185,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>45712</v>
       </c>
@@ -4203,7 +4202,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>45713</v>
       </c>
@@ -4220,7 +4219,7 @@
         <v>640000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>45715</v>
       </c>
@@ -4237,7 +4236,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
         <v>564</v>
       </c>
@@ -4254,7 +4253,7 @@
         <v>1040000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>45717</v>
       </c>
@@ -4271,7 +4270,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>45720</v>
       </c>
@@ -4288,7 +4287,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>45721</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>45722</v>
       </c>
@@ -4322,7 +4321,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>45723</v>
       </c>
@@ -4339,7 +4338,7 @@
         <v>1360000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>45725</v>
       </c>
@@ -4356,7 +4355,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>45726</v>
       </c>
@@ -4373,7 +4372,7 @@
         <v>870000</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>45729</v>
       </c>
@@ -4390,7 +4389,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>45730</v>
       </c>
@@ -4407,7 +4406,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>45733</v>
       </c>
@@ -4424,7 +4423,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>45734</v>
       </c>
@@ -4441,7 +4440,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>45735</v>
       </c>
@@ -4458,7 +4457,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>45736</v>
       </c>
@@ -4475,7 +4474,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>45737</v>
       </c>
@@ -4492,7 +4491,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>45738</v>
       </c>
@@ -4509,7 +4508,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>45741</v>
       </c>
@@ -4526,7 +4525,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>45742</v>
       </c>
@@ -4543,7 +4542,7 @@
         <v>680000</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>45743</v>
       </c>
@@ -4560,7 +4559,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>45746</v>
       </c>
@@ -4577,7 +4576,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>45747</v>
       </c>
@@ -4594,7 +4593,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>45748</v>
       </c>
@@ -4611,7 +4610,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>45751</v>
       </c>
@@ -4628,7 +4627,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>45752</v>
       </c>
@@ -4645,7 +4644,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>45753</v>
       </c>
@@ -4662,7 +4661,7 @@
         <v>1280000</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>45754</v>
       </c>
@@ -4679,7 +4678,7 @@
         <v>780000</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>45755</v>
       </c>
@@ -4696,7 +4695,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>45756</v>
       </c>
@@ -4713,7 +4712,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>45758</v>
       </c>
@@ -4730,7 +4729,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>45759</v>
       </c>
@@ -4747,7 +4746,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>45760</v>
       </c>
@@ -4764,7 +4763,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>45761</v>
       </c>
@@ -4781,7 +4780,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>45764</v>
       </c>
@@ -4798,7 +4797,7 @@
         <v>380000</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>45765</v>
       </c>
@@ -4815,7 +4814,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>45766</v>
       </c>
@@ -4832,7 +4831,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>45767</v>
       </c>
@@ -4849,7 +4848,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>45768</v>
       </c>
@@ -4866,7 +4865,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>45769</v>
       </c>
@@ -4883,7 +4882,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>45770</v>
       </c>
@@ -4900,7 +4899,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>45771</v>
       </c>
@@ -4917,7 +4916,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>45774</v>
       </c>
@@ -4934,7 +4933,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>45775</v>
       </c>
@@ -4951,7 +4950,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>45776</v>
       </c>
@@ -4968,7 +4967,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>45778</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>780000</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>45779</v>
       </c>
@@ -5002,7 +5001,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>45780</v>
       </c>
@@ -5019,7 +5018,7 @@
         <v>630000</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>45783</v>
       </c>
@@ -5036,7 +5035,7 @@
         <v>1020000</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>45784</v>
       </c>
@@ -5053,7 +5052,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>45787</v>
       </c>
@@ -5070,7 +5069,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>45788</v>
       </c>
@@ -5087,7 +5086,7 @@
         <v>990000</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>45789</v>
       </c>
@@ -5104,7 +5103,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>45790</v>
       </c>
@@ -5121,7 +5120,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>45791</v>
       </c>
@@ -5138,7 +5137,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>45792</v>
       </c>
@@ -5155,7 +5154,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>45793</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>45794</v>
       </c>
@@ -5189,7 +5188,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>45795</v>
       </c>
@@ -5206,7 +5205,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>45796</v>
       </c>
@@ -5223,7 +5222,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>45797</v>
       </c>
@@ -5240,7 +5239,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>45800</v>
       </c>
@@ -5257,7 +5256,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>45801</v>
       </c>
@@ -5274,7 +5273,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>45802</v>
       </c>
@@ -5291,7 +5290,7 @@
         <v>1120000</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>45805</v>
       </c>
@@ -5308,7 +5307,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>45808</v>
       </c>
@@ -5325,7 +5324,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>45811</v>
       </c>
@@ -5342,7 +5341,7 @@
         <v>760000</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>45813</v>
       </c>
@@ -5359,7 +5358,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>45814</v>
       </c>
@@ -5376,7 +5375,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>45815</v>
       </c>
@@ -5393,7 +5392,7 @@
         <v>840000</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>45817</v>
       </c>
@@ -5410,7 +5409,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>45818</v>
       </c>
@@ -5427,7 +5426,7 @@
         <v>840000</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>45820</v>
       </c>
@@ -5444,7 +5443,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
         <v>45821</v>
       </c>
@@ -5461,7 +5460,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1">
         <v>45822</v>
       </c>
@@ -5478,7 +5477,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1">
         <v>45823</v>
       </c>
@@ -5495,7 +5494,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
         <v>45824</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1">
         <v>45825</v>
       </c>
@@ -5529,7 +5528,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1">
         <v>45826</v>
       </c>
@@ -5546,7 +5545,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1">
         <v>45827</v>
       </c>
@@ -5563,7 +5562,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1">
         <v>45828</v>
       </c>
@@ -5580,7 +5579,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1">
         <v>45830</v>
       </c>
@@ -5597,7 +5596,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
         <v>45831</v>
       </c>
@@ -5614,7 +5613,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1">
         <v>45834</v>
       </c>
@@ -5631,7 +5630,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1">
         <v>45835</v>
       </c>
@@ -5648,7 +5647,7 @@
         <v>690000</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
         <v>45836</v>
       </c>
@@ -5665,7 +5664,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1">
         <v>45837</v>
       </c>
@@ -5682,7 +5681,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1">
         <v>45838</v>
       </c>
@@ -5699,7 +5698,7 @@
         <v>520000</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
         <v>45839</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>1360000</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1">
         <v>45840</v>
       </c>
@@ -5733,7 +5732,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1">
         <v>45841</v>
       </c>
@@ -5750,7 +5749,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
         <v>45844</v>
       </c>
@@ -5767,7 +5766,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1">
         <v>45845</v>
       </c>
@@ -5784,7 +5783,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1">
         <v>45848</v>
       </c>
@@ -5801,7 +5800,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
         <v>45849</v>
       </c>
@@ -5818,7 +5817,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1">
         <v>45850</v>
       </c>
@@ -5835,7 +5834,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1">
         <v>45851</v>
       </c>
@@ -5852,7 +5851,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
         <v>45854</v>
       </c>
@@ -5869,7 +5868,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1">
         <v>45855</v>
       </c>
@@ -5886,7 +5885,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1">
         <v>45856</v>
       </c>
@@ -5903,7 +5902,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
         <v>45857</v>
       </c>
@@ -5920,7 +5919,7 @@
         <v>520000</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="1">
         <v>45858</v>
       </c>
@@ -5937,7 +5936,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="1">
         <v>45859</v>
       </c>
@@ -5954,7 +5953,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
         <v>45860</v>
       </c>
@@ -5971,7 +5970,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1">
         <v>45861</v>
       </c>
@@ -5988,7 +5987,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1">
         <v>45864</v>
       </c>
@@ -6005,7 +6004,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1">
         <v>45865</v>
       </c>
@@ -6022,7 +6021,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1">
         <v>45866</v>
       </c>
@@ -6039,7 +6038,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="1">
         <v>45867</v>
       </c>
@@ -6056,7 +6055,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="1">
         <v>45870</v>
       </c>
@@ -6073,7 +6072,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="1">
         <v>45872</v>
       </c>
@@ -6090,7 +6089,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="1">
         <v>45873</v>
       </c>
@@ -6107,7 +6106,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="1">
         <v>45874</v>
       </c>
@@ -6124,7 +6123,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="1">
         <v>45875</v>
       </c>
@@ -6141,7 +6140,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="1">
         <v>45878</v>
       </c>
@@ -6158,7 +6157,7 @@
         <v>1040000</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="1">
         <v>45880</v>
       </c>
@@ -6175,7 +6174,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="1">
         <v>45881</v>
       </c>
@@ -6192,7 +6191,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="1">
         <v>45882</v>
       </c>
@@ -6209,7 +6208,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="1">
         <v>45883</v>
       </c>
@@ -6226,7 +6225,7 @@
         <v>930000</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="1">
         <v>45884</v>
       </c>
@@ -6243,7 +6242,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="1">
         <v>45885</v>
       </c>
@@ -6260,7 +6259,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="1">
         <v>45886</v>
       </c>
@@ -6277,7 +6276,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="1">
         <v>45887</v>
       </c>
@@ -6294,7 +6293,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" s="1">
         <v>45888</v>
       </c>
@@ -6311,7 +6310,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" s="1">
         <v>45889</v>
       </c>
@@ -6328,7 +6327,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" s="1">
         <v>45890</v>
       </c>
@@ -6345,7 +6344,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" s="1">
         <v>45891</v>
       </c>
@@ -6362,7 +6361,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="1">
         <v>45892</v>
       </c>
@@ -6379,7 +6378,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" s="1">
         <v>45893</v>
       </c>
@@ -6396,7 +6395,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" s="1">
         <v>45894</v>
       </c>
@@ -6413,7 +6412,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="1">
         <v>45895</v>
       </c>
@@ -6430,7 +6429,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" s="1">
         <v>45896</v>
       </c>
@@ -6447,7 +6446,7 @@
         <v>630000</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="1">
         <v>45897</v>
       </c>
@@ -6464,7 +6463,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="1">
         <v>45898</v>
       </c>
@@ -6481,7 +6480,7 @@
         <v>1360000</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="1">
         <v>45900</v>
       </c>
@@ -6498,7 +6497,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" s="1">
         <v>45901</v>
       </c>
@@ -6515,7 +6514,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="1">
         <v>45904</v>
       </c>
@@ -6532,7 +6531,7 @@
         <v>930000</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" s="1">
         <v>45905</v>
       </c>
@@ -6549,7 +6548,7 @@
         <v>1240000</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" s="1">
         <v>45906</v>
       </c>
@@ -6566,7 +6565,7 @@
         <v>570000</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" s="1">
         <v>45908</v>
       </c>
@@ -6583,7 +6582,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" s="1">
         <v>45909</v>
       </c>
@@ -6600,7 +6599,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" s="1">
         <v>45910</v>
       </c>
@@ -6617,7 +6616,7 @@
         <v>1120000</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" s="1">
         <v>45911</v>
       </c>
@@ -6634,7 +6633,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="1">
         <v>45912</v>
       </c>
@@ -6651,7 +6650,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1">
         <v>45913</v>
       </c>
@@ -6668,7 +6667,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1">
         <v>45914</v>
       </c>
@@ -6685,7 +6684,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" s="1">
         <v>45916</v>
       </c>
@@ -6702,7 +6701,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" s="1">
         <v>45917</v>
       </c>
@@ -6719,7 +6718,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" s="1">
         <v>45918</v>
       </c>
@@ -6736,7 +6735,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1">
         <v>45919</v>
       </c>
@@ -6753,7 +6752,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" s="1">
         <v>45920</v>
       </c>
@@ -6770,7 +6769,7 @@
         <v>1360000</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1">
         <v>45923</v>
       </c>
@@ -6787,7 +6786,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" s="1">
         <v>45924</v>
       </c>
@@ -6804,7 +6803,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1">
         <v>45925</v>
       </c>
@@ -6821,7 +6820,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1">
         <v>45926</v>
       </c>
@@ -6838,7 +6837,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1">
         <v>45928</v>
       </c>
@@ -6855,7 +6854,7 @@
         <v>690000</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" s="1">
         <v>45929</v>
       </c>
@@ -6872,7 +6871,7 @@
         <v>960000</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1">
         <v>45930</v>
       </c>
@@ -6889,7 +6888,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="1">
         <v>45932</v>
       </c>
@@ -6906,7 +6905,7 @@
         <v>420000</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1">
         <v>45933</v>
       </c>
@@ -6923,7 +6922,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" s="1">
         <v>45934</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1">
         <v>45935</v>
       </c>
@@ -6957,7 +6956,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" s="1">
         <v>45936</v>
       </c>
@@ -6974,7 +6973,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1">
         <v>45937</v>
       </c>
@@ -6991,7 +6990,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" s="1">
         <v>45939</v>
       </c>
@@ -7008,7 +7007,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1">
         <v>45941</v>
       </c>
@@ -7025,7 +7024,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" s="1">
         <v>45942</v>
       </c>
@@ -7042,7 +7041,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1">
         <v>45943</v>
       </c>
@@ -7059,7 +7058,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1">
         <v>45944</v>
       </c>
@@ -7076,7 +7075,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" s="1">
         <v>45947</v>
       </c>
@@ -7093,7 +7092,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1">
         <v>45948</v>
       </c>
@@ -7110,7 +7109,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" s="1">
         <v>45949</v>
       </c>
@@ -7127,7 +7126,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1">
         <v>45950</v>
       </c>
@@ -7144,7 +7143,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213" s="1">
         <v>45951</v>
       </c>
@@ -7161,7 +7160,7 @@
         <v>560000</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1">
         <v>45952</v>
       </c>
@@ -7178,7 +7177,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215" s="1">
         <v>45954</v>
       </c>
@@ -7195,7 +7194,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1">
         <v>45955</v>
       </c>
@@ -7212,7 +7211,7 @@
         <v>1280000</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217" s="1">
         <v>45956</v>
       </c>
@@ -7229,7 +7228,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" s="1">
         <v>45957</v>
       </c>
@@ -7246,7 +7245,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" s="1">
         <v>45958</v>
       </c>
@@ -7263,7 +7262,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220" s="1">
         <v>45959</v>
       </c>
@@ -7280,7 +7279,7 @@
         <v>660000</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221" s="1">
         <v>45960</v>
       </c>
@@ -7297,7 +7296,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222" s="1">
         <v>45963</v>
       </c>
@@ -7314,7 +7313,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" s="1">
         <v>45964</v>
       </c>
@@ -7331,7 +7330,7 @@
         <v>920000</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224" s="1">
         <v>45967</v>
       </c>
@@ -7348,7 +7347,7 @@
         <v>1040000</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" s="1">
         <v>45968</v>
       </c>
@@ -7365,7 +7364,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" s="1">
         <v>45969</v>
       </c>
@@ -7382,7 +7381,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227" s="1">
         <v>45970</v>
       </c>
@@ -7399,7 +7398,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228" s="1">
         <v>45972</v>
       </c>
@@ -7416,7 +7415,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229" s="1">
         <v>45974</v>
       </c>
@@ -7433,7 +7432,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230" s="1">
         <v>45975</v>
       </c>
@@ -7450,7 +7449,7 @@
         <v>1040000</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231" s="1">
         <v>45976</v>
       </c>
@@ -7467,7 +7466,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" s="1">
         <v>45978</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" s="1">
         <v>45979</v>
       </c>
@@ -7501,7 +7500,7 @@
         <v>540000</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234" s="1">
         <v>45980</v>
       </c>
@@ -7518,7 +7517,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235" s="1">
         <v>45981</v>
       </c>
@@ -7535,7 +7534,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236" s="1">
         <v>45982</v>
       </c>
@@ -7552,7 +7551,7 @@
         <v>680000</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237" s="1">
         <v>45983</v>
       </c>
@@ -7569,7 +7568,7 @@
         <v>460000</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238" s="1">
         <v>45984</v>
       </c>
@@ -7586,7 +7585,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" s="1">
         <v>45986</v>
       </c>
@@ -7603,7 +7602,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" s="1">
         <v>45987</v>
       </c>
@@ -7620,7 +7619,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241" s="1">
         <v>45988</v>
       </c>
@@ -7637,7 +7636,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242" s="1">
         <v>45989</v>
       </c>
@@ -7654,7 +7653,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" s="1">
         <v>45990</v>
       </c>
@@ -7671,7 +7670,7 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244" s="1">
         <v>45991</v>
       </c>
@@ -7688,7 +7687,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A245" s="1">
         <v>45992</v>
       </c>
@@ -7705,7 +7704,7 @@
         <v>760000</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" s="1">
         <v>45993</v>
       </c>
@@ -7722,7 +7721,7 @@
         <v>680000</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" s="1">
         <v>45994</v>
       </c>
@@ -7739,7 +7738,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A248" s="1">
         <v>45995</v>
       </c>
@@ -7756,7 +7755,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249" s="1">
         <v>45996</v>
       </c>
@@ -7773,7 +7772,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250" s="1">
         <v>45997</v>
       </c>
@@ -7790,7 +7789,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251" s="1">
         <v>45998</v>
       </c>
@@ -7807,7 +7806,7 @@
         <v>580000</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252" s="1">
         <v>46001</v>
       </c>
@@ -7824,7 +7823,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" s="1">
         <v>46004</v>
       </c>
@@ -7841,7 +7840,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" s="1">
         <v>46005</v>
       </c>
@@ -7858,7 +7857,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255" s="1">
         <v>46007</v>
       </c>
@@ -7875,7 +7874,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256" s="1">
         <v>46008</v>
       </c>
